--- a/nr-doc-core-adverse-event/ig/ValueSet-fr-core-vs-oragnization-code-tarif-tnjp.xlsx
+++ b/nr-doc-core-adverse-event/ig/ValueSet-fr-core-vs-oragnization-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:19:58+00:00</t>
+    <t>2026-06-29T12:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-adverse-event/ig/ValueSet-fr-core-vs-oragnization-code-tarif-tnjp.xlsx
+++ b/nr-doc-core-adverse-event/ig/ValueSet-fr-core-vs-oragnization-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:41:53+00:00</t>
+    <t>2026-07-21T12:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-adverse-event/ig/ValueSet-fr-core-vs-oragnization-code-tarif-tnjp.xlsx
+++ b/nr-doc-core-adverse-event/ig/ValueSet-fr-core-vs-oragnization-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T12:27:37+00:00</t>
+    <t>2026-07-30T09:44:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-adverse-event/ig/ValueSet-fr-core-vs-oragnization-code-tarif-tnjp.xlsx
+++ b/nr-doc-core-adverse-event/ig/ValueSet-fr-core-vs-oragnization-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:44:31+00:00</t>
+    <t>2026-07-30T14:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-adverse-event/ig/ValueSet-fr-core-vs-oragnization-code-tarif-tnjp.xlsx
+++ b/nr-doc-core-adverse-event/ig/ValueSet-fr-core-vs-oragnization-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:18:46+00:00</t>
+    <t>2026-07-30T14:33:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-adverse-event/ig/ValueSet-fr-core-vs-oragnization-code-tarif-tnjp.xlsx
+++ b/nr-doc-core-adverse-event/ig/ValueSet-fr-core-vs-oragnization-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:33:32+00:00</t>
+    <t>2026-07-30T14:45:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-adverse-event/ig/ValueSet-fr-core-vs-oragnization-code-tarif-tnjp.xlsx
+++ b/nr-doc-core-adverse-event/ig/ValueSet-fr-core-vs-oragnization-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:45:27+00:00</t>
+    <t>2026-07-30T14:49:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
